--- a/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20250328120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2025-03-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,6 +120,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -129,13 +132,61 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
     <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>departement</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#departement</t>
+  </si>
+  <si>
+    <t>Département  de la commune</t>
+  </si>
+  <si>
+    <t>Coding</t>
   </si>
 </sst>
 </file>
@@ -431,7 +482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -452,36 +503,98 @@
       <c r="A2" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>42</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250328120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R13-CommuneOM.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
